--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486664_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486664_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8627</v>
+        <v>4.6243</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6377</v>
+        <v>1.9207</v>
       </c>
       <c r="F2" t="n">
-        <v>3.225</v>
+        <v>2.7035</v>
       </c>
       <c r="G2" t="n">
         <v>4.024</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1903</v>
+        <v>0.9518</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9648</v>
+        <v>0.2478</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2255</v>
+        <v>0.704</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.488</v>
+        <v>3.7985</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4089</v>
+        <v>0.8436</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0791</v>
+        <v>2.9549</v>
       </c>
       <c r="G3" t="n">
         <v>3.27</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2414</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.772</v>
+        <v>0.2066</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4694</v>
+        <v>0.3452</v>
       </c>
       <c r="V3" t="n">
         <v>0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5176</v>
+        <v>1.9671</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2881</v>
+        <v>-0.764</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8056</v>
+        <v>2.7311</v>
       </c>
       <c r="G4" t="n">
         <v>1.4897</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1437</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4142</v>
+        <v>0.1099</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5578</v>
+        <v>0.4833</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4655</v>
+        <v>1.7717</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1858</v>
+        <v>1.3926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2797</v>
+        <v>0.379</v>
       </c>
       <c r="G5" t="n">
         <v>0.9304</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4303</v>
+        <v>-0.1241</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>-0.0139</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2096</v>
+        <v>-0.1102</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9321</v>
+        <v>1.3914</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.663</v>
+        <v>-0.3528</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5952</v>
+        <v>1.7442</v>
       </c>
       <c r="G6" t="n">
         <v>1.0394</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5626</v>
+        <v>-0.1034</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3863</v>
+        <v>-0.076</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1763</v>
+        <v>-0.0274</v>
       </c>
       <c r="V6" t="n">
         <v>1.2277</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3365</v>
+        <v>-0.1586</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0205</v>
+        <v>0.083</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3161</v>
+        <v>-0.2416</v>
       </c>
       <c r="G7" t="n">
         <v>0.2963</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4744</v>
+        <v>-0.2965</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.364</v>
+        <v>-0.2895</v>
       </c>
       <c r="V7" t="n">
         <v>0.6138</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3672</v>
+        <v>-0.6237</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0647</v>
+        <v>-2.2715</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6975</v>
+        <v>1.6478</v>
       </c>
       <c r="G8" t="n">
         <v>0.9291</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3255</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>0.1515</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0329</v>
+        <v>-0.0825</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6565</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4939</v>
+        <v>-0.7504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4422</v>
+        <v>0.2353</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9857</v>
       </c>
       <c r="G9" t="n">
         <v>0.6182</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1434</v>
+        <v>-0.3999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4466</v>
+        <v>-0.4962</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1271</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9574</v>
+        <v>-0.8411</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3486</v>
+        <v>-1.9542</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3912</v>
+        <v>1.1131</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2457</v>
+        <v>0.0236</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3519</v>
+        <v>-0.9869</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1063</v>
+        <v>1.0105</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6657999999999999</v>
+        <v>0.1977</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6274</v>
+        <v>-1.1927</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0384</v>
+        <v>1.3904</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4201</v>
+        <v>-0.174</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2755</v>
+        <v>0.2058</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1447</v>
+        <v>-0.3799</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1325</v>
+        <v>-0.386</v>
       </c>
       <c r="T10" t="n">
-        <v>0.248</v>
+        <v>-0.2211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3805</v>
+        <v>-0.165</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3833</v>
+        <v>-0.9352</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5703</v>
+        <v>-2.5002</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1871</v>
+        <v>1.565</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4221</v>
+        <v>-0.2457</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.3519</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4815</v>
+        <v>0.1063</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7042</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>-0.6274</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0384</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2821</v>
+        <v>0.4201</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2763</v>
+        <v>0.2755</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5583</v>
+        <v>0.1447</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7031</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0892</v>
+        <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4563</v>
+        <v>-0.1103</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9375</v>
+        <v>0.0964</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5188</v>
+        <v>-0.2067</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9775</v>
+        <v>-2.0535</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8919</v>
+        <v>-3.1909</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9145</v>
+        <v>1.1374</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0236</v>
+        <v>-0.4221</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9869</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0105</v>
+        <v>0.4815</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1977</v>
+        <v>-0.7042</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1927</v>
+        <v>-0.6274</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3904</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.174</v>
+        <v>0.2821</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2058</v>
+        <v>-0.2763</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3799</v>
+        <v>0.5583</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1931</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9308</v>
+        <v>-3.0892</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5224</v>
+        <v>0.7861</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1588</v>
+        <v>0.317</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3636</v>
+        <v>0.4692</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6585</v>
+        <v>-2.547</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3178</v>
+        <v>-1.3801</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3407</v>
+        <v>-1.1669</v>
       </c>
       <c r="G13" t="n">
         <v>0.2531</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2632</v>
+        <v>-0.1516</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1588</v>
+        <v>-0.2211</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1044</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4554</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0916</v>
+        <v>5.643500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.490300000000001</v>
+        <v>-7.938499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5821</v>
+        <v>13.5818</v>
       </c>
       <c r="G14" t="n">
         <v>12.206</v>
       </c>
       <c r="H14" t="n">
-        <v>2.066900000000001</v>
+        <v>2.0669</v>
       </c>
       <c r="I14" t="n">
         <v>10.1392</v>
@@ -1528,13 +1528,13 @@
         <v>10.6259</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9201</v>
+        <v>1.920100000000001</v>
       </c>
       <c r="N14" t="n">
         <v>2.4064</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4864999999999999</v>
+        <v>-0.4865</v>
       </c>
       <c r="P14" t="n">
         <v>-6.757700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>14.4809</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8284000000000005</v>
+        <v>1.3802</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1347</v>
+        <v>0.6866000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6936</v>
+        <v>0.6936999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1851</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.855</v>
+        <v>6.0244</v>
       </c>
       <c r="E15" t="n">
-        <v>4.749</v>
+        <v>5.2661</v>
       </c>
       <c r="F15" t="n">
-        <v>1.106</v>
+        <v>0.7583</v>
       </c>
       <c r="G15" t="n">
         <v>4.452</v>
@@ -1624,13 +1624,13 @@
         <v>3.4754</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3971</v>
+        <v>-0.2276</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.311</v>
       </c>
       <c r="U15" t="n">
-        <v>0.431</v>
+        <v>0.0834</v>
       </c>
       <c r="V15" t="n">
         <v>0.4485</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1811</v>
+        <v>1.4873</v>
       </c>
       <c r="E16" t="n">
-        <v>0.103</v>
+        <v>0.3098</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0781</v>
+        <v>1.1774</v>
       </c>
       <c r="G16" t="n">
         <v>1.3509</v>
@@ -1702,13 +1702,13 @@
         <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3476</v>
+        <v>-0.0414</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V16" t="n">
         <v>0.3709</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>M. SOW SOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9681</v>
+        <v>0.7995</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2679</v>
+        <v>0.2346</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7002</v>
+        <v>0.5649</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3227</v>
+        <v>-0.5657</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.048</v>
+        <v>1.1998</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3707</v>
+        <v>-1.7656</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3785</v>
+        <v>0.3037</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2971</v>
+        <v>0.9932</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0814</v>
+        <v>-0.6895</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0558</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3451</v>
+        <v>0.2066</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2893</v>
+        <v>-1.0761</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2592</v>
+        <v>0.0137</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>-0.0692</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1768</v>
+        <v>0.0829</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOW SOW</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9567</v>
+        <v>0.5296</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4414</v>
+        <v>-0.1458</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5153</v>
+        <v>0.6754</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5657</v>
+        <v>0.3227</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1998</v>
+        <v>-0.048</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7656</v>
+        <v>0.3707</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3037</v>
+        <v>0.3785</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9932</v>
+        <v>0.2971</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6895</v>
+        <v>0.0814</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.0558</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2066</v>
+        <v>-0.3451</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0761</v>
+        <v>0.2893</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1709</v>
+        <v>-0.1793</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1377</v>
+        <v>-0.3312</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0332</v>
+        <v>0.1519</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1004</v>
+        <v>-0.8369</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0248</v>
+        <v>-4.4384</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9244</v>
+        <v>3.6015</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1542</v>
@@ -1936,13 +1936,13 @@
         <v>2.8962</v>
       </c>
       <c r="S19" t="n">
-        <v>0.833</v>
+        <v>0.0965</v>
       </c>
       <c r="T19" t="n">
-        <v>0.165</v>
+        <v>-0.2487</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6681</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7792</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3948</v>
+        <v>-1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2436</v>
+        <v>-2.9333</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8488</v>
+        <v>1.9233</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3617</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8054</v>
+        <v>-0.4206</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8277</v>
+        <v>-0.5175</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0224</v>
+        <v>0.0969</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.049</v>
+        <v>-1.2546</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3822</v>
+        <v>-1.7617</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3332</v>
+        <v>0.5071</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3659</v>
@@ -2092,13 +2092,13 @@
         <v>3.6685</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4565</v>
+        <v>-0.6622</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9936</v>
+        <v>-0.3731</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4629</v>
+        <v>-0.2891</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7366</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7742</v>
+        <v>-2.8694</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4849</v>
+        <v>-2.7803</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2893</v>
+        <v>-0.0891</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1131</v>
+        <v>-3.305</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7996</v>
+        <v>-0.2486</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3135</v>
+        <v>-3.0564</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1881</v>
+        <v>-1.8215</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3508</v>
+        <v>0.1655</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1628</v>
+        <v>-1.9871</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.925</v>
+        <v>-1.4835</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5513</v>
+        <v>-0.4142</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4763</v>
+        <v>-1.0693</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8962</v>
+        <v>-1.1585</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4616</v>
+        <v>-0.0208</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5993</v>
+        <v>0.1997</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1377</v>
+        <v>-0.2205</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3505</v>
+        <v>-0.1228</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3505</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.792</v>
+        <v>-3.4774</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5043</v>
+        <v>-3.3123</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2877</v>
+        <v>-0.1651</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.305</v>
+        <v>-2.1131</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2486</v>
+        <v>-0.7996</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0564</v>
+        <v>-1.3135</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8215</v>
+        <v>-1.1881</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1655</v>
+        <v>-1.3508</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9871</v>
+        <v>0.1628</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4835</v>
+        <v>-0.925</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4142</v>
+        <v>0.5513</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0693</v>
+        <v>-1.4763</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5792</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1585</v>
+        <v>-2.8962</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9434</v>
+        <v>0.7584</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5243</v>
+        <v>0.772</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4191</v>
+        <v>-0.0136</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1228</v>
+        <v>-1.3505</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1228</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9421</v>
+        <v>-4.484</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5035</v>
+        <v>-4.0206</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4386</v>
+        <v>-0.4634</v>
       </c>
       <c r="G24" t="n">
         <v>-8.466100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>2.8962</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3969</v>
+        <v>-0.145</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7716</v>
+        <v>0.2545</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3747</v>
+        <v>-0.3995</v>
       </c>
       <c r="V24" t="n">
         <v>3.3548</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0916</v>
+        <v>-5.0915</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.582</v>
+        <v>-13.5819</v>
       </c>
       <c r="F25" t="n">
-        <v>8.490400000000001</v>
+        <v>8.4903</v>
       </c>
       <c r="G25" t="n">
         <v>-12.2061</v>
@@ -2389,7 +2389,7 @@
         <v>-10.2861</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3396000000000001</v>
+        <v>0.3396</v>
       </c>
       <c r="O25" t="n">
         <v>-10.6257</v>
@@ -2404,13 +2404,13 @@
         <v>21.2386</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8284</v>
+        <v>-0.8283</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6935000000000001</v>
+        <v>-0.6936</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1345999999999999</v>
+        <v>-0.1347000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>1.1851</v>
